--- a/data/trans_dic/IP15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 34,2</t>
+          <t>21,12; 34,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,53</t>
+          <t>19,16; 30,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 26,52</t>
+          <t>15,68; 26,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 38,02</t>
+          <t>19,54; 37,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 31,44</t>
+          <t>18,82; 30,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,75; 32,61</t>
+          <t>20,7; 33,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 25,6</t>
+          <t>14,26; 24,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,84; 46,44</t>
+          <t>27,48; 46,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,93; 30,94</t>
+          <t>21,24; 30,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,19; 29,85</t>
+          <t>21,86; 30,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 24,42</t>
+          <t>16,01; 23,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,59; 39,25</t>
+          <t>26,02; 39,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 21,04</t>
+          <t>13,74; 21,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 27,78</t>
+          <t>18,49; 27,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 24,81</t>
+          <t>15,95; 24,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,15; 36,26</t>
+          <t>23,21; 35,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,88</t>
+          <t>16,3; 24,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 29,52</t>
+          <t>20,71; 29,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 20,56</t>
+          <t>12,62; 20,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 32,85</t>
+          <t>21,56; 33,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 21,67</t>
+          <t>16,06; 21,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,08; 27,56</t>
+          <t>20,86; 27,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 21,36</t>
+          <t>15,71; 21,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 32,31</t>
+          <t>23,9; 32,4</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,91; 23,74</t>
+          <t>12,62; 23,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 24,52</t>
+          <t>14,09; 24,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 24,24</t>
+          <t>14,84; 24,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 28,23</t>
+          <t>16,9; 27,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,78; 21,94</t>
+          <t>11,5; 22,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 23,35</t>
+          <t>13,1; 23,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,12; 22,62</t>
+          <t>13,21; 22,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,25; 26,95</t>
+          <t>17,12; 27,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,14</t>
+          <t>13,67; 21,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 22,04</t>
+          <t>15,07; 22,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,67; 22,21</t>
+          <t>15,28; 22,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 25,6</t>
+          <t>18,26; 26,21</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 20,44</t>
+          <t>11,6; 20,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 20,95</t>
+          <t>11,56; 20,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,7</t>
+          <t>8,41; 17,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 51,45</t>
+          <t>18,67; 48,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 23,78</t>
+          <t>15,03; 24,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 18,84</t>
+          <t>10,21; 18,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 18,27</t>
+          <t>9,0; 17,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 27,33</t>
+          <t>16,4; 26,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,88</t>
+          <t>14,05; 20,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,96</t>
+          <t>12,17; 18,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,24</t>
+          <t>10,19; 16,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 38,49</t>
+          <t>19,58; 36,27</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,79</t>
+          <t>16,3; 20,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,23</t>
+          <t>18,31; 23,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 20,56</t>
+          <t>15,78; 20,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,39; 37,97</t>
+          <t>22,44; 38,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,63; 22,56</t>
+          <t>17,64; 22,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,46</t>
+          <t>18,66; 23,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,82</t>
+          <t>14,4; 19,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,87; 26,87</t>
+          <t>21,35; 27,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 20,86</t>
+          <t>17,47; 20,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 22,72</t>
+          <t>19,25; 22,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,91</t>
+          <t>15,79; 18,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 31,08</t>
+          <t>22,75; 30,58</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>29035</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27033</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22356</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>58690</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74923</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51009</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>38340</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>22422; 36816</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28119; 44621</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20643; 34806</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11238; 21447</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22841; 37251</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30224; 48358</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17703; 30786</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16884; 28395</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>48341; 70347</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>63989; 88398</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>40945; 61205</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>30954; 46664</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>43221</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54165</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42239</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46623</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>48984</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>94181</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>121529</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95607</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>34787; 54365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43694; 65161</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33585; 52399</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36978; 56972</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>41367; 61874</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>55708; 79189</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>32558; 53339</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39208; 60254</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>81443; 109345</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>105398; 137787</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>73626; 100177</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>81524; 110528</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22507</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29870</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36124</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37151</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46169</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>46373</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57785</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69570</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>83320</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16098; 30190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22133; 38291</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28034; 45783</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28666; 46624</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>16277; 31296</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20678; 36509</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24918; 41972</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>36386; 58658</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>36775; 57437</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>47446; 70175</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>57683; 83689</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>69766; 100122</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>30543</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27169</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22065</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>64692</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69981</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52037</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>44823</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>142649</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>22509; 39077</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19810; 35830</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14573; 30078</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51437; 133249</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30976; 49537</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18302; 33082</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>15662; 31072</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>50104; 80328</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>56226; 81399</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>42653; 64645</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>35409; 56724</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>113758; 210703</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>147701</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>127461</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>177715</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>182201</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>306275</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>250737</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>359916</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>110980; 142532</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>130280; 167322</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>111129; 144884</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148523; 256457</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>127498; 161419</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>140344; 177591</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>107274; 142274</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>162543; 206332</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>245290; 292494</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>281654; 332147</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>228851; 273319</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>323800; 435188</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 34,68</t>
+          <t>21,01; 35,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 30,4</t>
+          <t>19,29; 31,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,68; 26,44</t>
+          <t>15,47; 26,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 37,29</t>
+          <t>19,37; 37,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 30,69</t>
+          <t>18,58; 31,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,7; 33,12</t>
+          <t>20,35; 33,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 24,79</t>
+          <t>14,01; 26,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 46,21</t>
+          <t>27,8; 46,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 30,91</t>
+          <t>20,62; 30,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,86; 30,2</t>
+          <t>21,1; 29,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 23,93</t>
+          <t>16,18; 23,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,02; 39,23</t>
+          <t>25,43; 38,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,74; 21,47</t>
+          <t>13,49; 20,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 27,58</t>
+          <t>18,52; 27,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 24,89</t>
+          <t>15,92; 24,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,21; 35,76</t>
+          <t>23,96; 36,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 24,38</t>
+          <t>16,46; 24,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 29,44</t>
+          <t>20,8; 29,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 20,67</t>
+          <t>12,98; 20,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,56; 33,13</t>
+          <t>21,71; 33,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 21,57</t>
+          <t>16,01; 21,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 27,27</t>
+          <t>21,08; 27,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 21,38</t>
+          <t>15,41; 21,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,9; 32,4</t>
+          <t>24,15; 32,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,62; 23,67</t>
+          <t>12,97; 24,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 24,38</t>
+          <t>14,34; 24,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 24,24</t>
+          <t>14,5; 24,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 27,5</t>
+          <t>17,07; 27,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 22,11</t>
+          <t>12,4; 22,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 23,14</t>
+          <t>12,66; 23,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 22,26</t>
+          <t>13,33; 22,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 27,61</t>
+          <t>16,68; 27,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 21,35</t>
+          <t>13,91; 21,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 22,29</t>
+          <t>14,9; 22,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,17</t>
+          <t>15,31; 21,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 26,21</t>
+          <t>18,24; 25,65</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,13</t>
+          <t>11,72; 19,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 20,91</t>
+          <t>12,06; 20,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 17,36</t>
+          <t>8,93; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 48,37</t>
+          <t>18,92; 48,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 24,04</t>
+          <t>14,98; 23,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 18,46</t>
+          <t>9,85; 18,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 17,85</t>
+          <t>9,49; 17,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 26,3</t>
+          <t>16,55; 26,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 20,34</t>
+          <t>14,79; 20,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,17; 18,44</t>
+          <t>11,91; 18,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,33</t>
+          <t>9,89; 15,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 36,27</t>
+          <t>19,41; 37,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 20,93</t>
+          <t>16,22; 20,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,31; 23,52</t>
+          <t>18,36; 23,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,57</t>
+          <t>15,79; 20,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 38,75</t>
+          <t>22,28; 37,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,34</t>
+          <t>17,66; 22,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,62</t>
+          <t>18,72; 23,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,1</t>
+          <t>14,51; 19,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,1</t>
+          <t>21,02; 27,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 20,84</t>
+          <t>17,57; 20,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,25; 22,7</t>
+          <t>19,11; 22,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 18,86</t>
+          <t>15,71; 18,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 30,58</t>
+          <t>22,79; 29,94</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22422; 36816</t>
+          <t>22308; 37271</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28119; 44621</t>
+          <t>28310; 45973</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20643; 34806</t>
+          <t>20368; 35287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11238; 21447</t>
+          <t>11138; 21341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22841; 37251</t>
+          <t>22558; 37815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30224; 48358</t>
+          <t>29712; 48705</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17703; 30786</t>
+          <t>17401; 32286</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16884; 28395</t>
+          <t>17079; 28358</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48341; 70347</t>
+          <t>46930; 69123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63989; 88398</t>
+          <t>61769; 86717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40945; 61205</t>
+          <t>41383; 60384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30954; 46664</t>
+          <t>30254; 45579</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34787; 54365</t>
+          <t>34164; 52629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43694; 65161</t>
+          <t>43749; 65646</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33585; 52399</t>
+          <t>33517; 52131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36978; 56972</t>
+          <t>38176; 58238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41367; 61874</t>
+          <t>41772; 62228</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55708; 79189</t>
+          <t>55951; 79910</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32558; 53339</t>
+          <t>33485; 53220</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39208; 60254</t>
+          <t>39473; 60692</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81443; 109345</t>
+          <t>81157; 109185</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105398; 137787</t>
+          <t>106516; 137901</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73626; 100177</t>
+          <t>72210; 99177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81524; 110528</t>
+          <t>82400; 110349</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16098; 30190</t>
+          <t>16549; 31013</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22133; 38291</t>
+          <t>22528; 38803</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28034; 45783</t>
+          <t>27391; 45506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28666; 46624</t>
+          <t>28939; 46699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16277; 31296</t>
+          <t>17554; 31558</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20678; 36509</t>
+          <t>19983; 36360</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24918; 41972</t>
+          <t>25142; 41868</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36386; 58658</t>
+          <t>35438; 58380</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36775; 57437</t>
+          <t>37436; 57088</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47446; 70175</t>
+          <t>46910; 69952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57683; 83689</t>
+          <t>57797; 81412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69766; 100122</t>
+          <t>69693; 97982</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22509; 39077</t>
+          <t>22751; 38596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19810; 35830</t>
+          <t>20666; 35529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14573; 30078</t>
+          <t>15473; 29764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51437; 133249</t>
+          <t>52113; 134435</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30976; 49537</t>
+          <t>30869; 49153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18302; 33082</t>
+          <t>17660; 32342</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15662; 31072</t>
+          <t>16519; 30977</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50104; 80328</t>
+          <t>50560; 80893</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56226; 81399</t>
+          <t>59193; 83611</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42653; 64645</t>
+          <t>41737; 64387</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35409; 56724</t>
+          <t>34362; 54721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>113758; 210703</t>
+          <t>112737; 220506</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>110980; 142532</t>
+          <t>110452; 142934</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130280; 167322</t>
+          <t>130633; 166963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111129; 144884</t>
+          <t>111243; 143709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148523; 256457</t>
+          <t>147455; 245221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>127498; 161419</t>
+          <t>127646; 162371</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140344; 177591</t>
+          <t>140740; 177977</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107274; 142274</t>
+          <t>108085; 141931</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162543; 206332</t>
+          <t>160032; 206571</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>245290; 292494</t>
+          <t>246620; 293691</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281654; 332147</t>
+          <t>279624; 331255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>228851; 273319</t>
+          <t>227717; 273513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>323800; 435188</t>
+          <t>324265; 426090</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26,32%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>20,53%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,79%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 35,11</t>
+          <t>18,69; 31,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 31,33</t>
+          <t>20,75; 32,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 26,8</t>
+          <t>14,07; 25,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 37,11</t>
+          <t>26,28; 44,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,58; 31,15</t>
+          <t>20,5; 34,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 33,36</t>
+          <t>19,71; 30,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 26,0</t>
+          <t>15,41; 26,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 46,15</t>
+          <t>19,41; 37,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 30,38</t>
+          <t>21,93; 30,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 29,62</t>
+          <t>21,19; 29,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 23,6</t>
+          <t>16,11; 24,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,43; 38,32</t>
+          <t>24,16; 37,43</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>17,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,06%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 20,78</t>
+          <t>16,31; 24,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 27,79</t>
+          <t>20,86; 29,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,92; 24,76</t>
+          <t>13,13; 20,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 36,56</t>
+          <t>20,7; 32,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 24,52</t>
+          <t>13,4; 21,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,8; 29,71</t>
+          <t>18,13; 27,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 20,62</t>
+          <t>15,96; 24,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,71; 33,38</t>
+          <t>22,77; 34,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,54</t>
+          <t>15,97; 21,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,08; 27,29</t>
+          <t>21,08; 27,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 21,17</t>
+          <t>15,52; 21,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,15; 32,35</t>
+          <t>23,03; 31,03</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17,65%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 24,32</t>
+          <t>11,78; 21,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 24,71</t>
+          <t>13,11; 23,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 24,09</t>
+          <t>13,12; 22,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 27,54</t>
+          <t>16,72; 27,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 22,3</t>
+          <t>12,91; 23,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 23,04</t>
+          <t>14,34; 24,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 22,2</t>
+          <t>14,56; 24,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 27,47</t>
+          <t>16,84; 27,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 21,22</t>
+          <t>13,77; 21,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 22,22</t>
+          <t>15,09; 22,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,57</t>
+          <t>15,67; 22,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,24; 25,65</t>
+          <t>18,33; 25,72</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,73%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 19,89</t>
+          <t>14,79; 23,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,74</t>
+          <t>10,26; 18,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 17,17</t>
+          <t>9,45; 18,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 48,8</t>
+          <t>16,91; 27,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 23,85</t>
+          <t>11,93; 20,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,04</t>
+          <t>11,68; 20,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 17,8</t>
+          <t>8,8; 17,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 26,48</t>
+          <t>15,56; 24,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 20,9</t>
+          <t>14,71; 20,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,37</t>
+          <t>11,82; 17,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,75</t>
+          <t>10,07; 16,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 37,96</t>
+          <t>17,16; 24,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,99</t>
+          <t>17,63; 22,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,47</t>
+          <t>18,59; 23,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,4</t>
+          <t>14,34; 18,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 37,05</t>
+          <t>20,52; 26,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 22,47</t>
+          <t>16,07; 20,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 23,67</t>
+          <t>18,26; 23,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,06</t>
+          <t>15,72; 20,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 27,14</t>
+          <t>19,99; 25,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,92</t>
+          <t>17,66; 20,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,11; 22,64</t>
+          <t>19,17; 22,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,87</t>
+          <t>15,61; 18,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,94</t>
+          <t>21,28; 25,44</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17432</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>36498</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22308; 37271</t>
+          <t>22688; 38163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28310; 45973</t>
+          <t>30299; 47601</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20368; 35287</t>
+          <t>17475; 31789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11138; 21341</t>
+          <t>13281; 22565</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22558; 37815</t>
+          <t>21766; 36311</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29712; 48705</t>
+          <t>28930; 44806</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17401; 32286</t>
+          <t>20289; 34909</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17079; 28358</t>
+          <t>10112; 19367</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46930; 69123</t>
+          <t>49894; 70402</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61769; 86717</t>
+          <t>62042; 87373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41383; 60384</t>
+          <t>41200; 62463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30254; 45579</t>
+          <t>24798; 38417</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34164; 52629</t>
+          <t>41380; 63124</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43749; 65646</t>
+          <t>56106; 79414</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33517; 52131</t>
+          <t>33879; 53046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38176; 58238</t>
+          <t>32476; 50656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41772; 62228</t>
+          <t>33921; 53266</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55951; 79910</t>
+          <t>42842; 65626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33485; 53220</t>
+          <t>33605; 52224</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39473; 60692</t>
+          <t>33139; 49823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81157; 109185</t>
+          <t>80974; 109873</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106516; 137901</t>
+          <t>106511; 139235</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72210; 99177</t>
+          <t>72720; 100088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82400; 110349</t>
+          <t>69642; 93829</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16549; 31013</t>
+          <t>16676; 31049</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22528; 38803</t>
+          <t>20687; 36845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27391; 45506</t>
+          <t>24733; 42651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28939; 46699</t>
+          <t>33470; 54230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17554; 31558</t>
+          <t>16466; 30278</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19983; 36360</t>
+          <t>22518; 38503</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25142; 41868</t>
+          <t>27504; 45794</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35438; 58380</t>
+          <t>29276; 48258</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37436; 57088</t>
+          <t>37042; 56869</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46910; 69952</t>
+          <t>47507; 69378</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57797; 81412</t>
+          <t>59158; 83847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69693; 97982</t>
+          <t>68525; 96183</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22751; 38596</t>
+          <t>30481; 49000</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20666; 35529</t>
+          <t>18393; 33770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15473; 29764</t>
+          <t>16449; 31792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52113; 134435</t>
+          <t>49495; 80058</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30869; 49153</t>
+          <t>23146; 39674</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17660; 32342</t>
+          <t>20017; 35892</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16519; 30977</t>
+          <t>15258; 30679</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50560; 80893</t>
+          <t>39917; 63958</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59193; 83611</t>
+          <t>58847; 83544</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41737; 64387</t>
+          <t>41453; 62972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34362; 54721</t>
+          <t>34993; 56398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>112737; 220506</t>
+          <t>94233; 132031</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>226</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>110452; 142934</t>
+          <t>127434; 163024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130633; 166963</t>
+          <t>139830; 176392</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111243; 143709</t>
+          <t>106791; 140198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147455; 245221</t>
+          <t>143688; 185319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>127646; 162371</t>
+          <t>109450; 141613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140740; 177977</t>
+          <t>129929; 165279</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108085; 141931</t>
+          <t>110759; 144834</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>160032; 206571</t>
+          <t>125557; 161697</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>246620; 293691</t>
+          <t>247844; 292802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>279624; 331255</t>
+          <t>280503; 332508</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227717; 273513</t>
+          <t>226261; 274110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>324265; 426090</t>
+          <t>282577; 337946</t>
         </is>
       </c>
     </row>
